--- a/data/trans_dic/IP13-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP13-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,16%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>7,65%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,4%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 14,06</t>
+          <t>1,13; 10,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 16,07</t>
+          <t>6,41; 20,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,43</t>
+          <t>4,41; 18,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,6</t>
+          <t>0,0; 8,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,2</t>
+          <t>3,12; 14,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,57; 21,15</t>
+          <t>2,74; 15,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 18,0</t>
+          <t>0,0; 8,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,41</t>
+          <t>2,0; 11,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,28</t>
+          <t>2,54; 9,39</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 15,69</t>
+          <t>6,27; 16,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 11,36</t>
+          <t>3,14; 10,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,85</t>
+          <t>1,55; 7,65</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,09%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,17%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>9,09%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>10,97%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,48%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,54</t>
+          <t>3,53; 11,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 14,15</t>
+          <t>7,37; 17,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,42; 16,52</t>
+          <t>3,01; 10,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,84</t>
+          <t>3,32; 11,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,85</t>
+          <t>3,1; 10,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 17,38</t>
+          <t>5,29; 14,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 10,9</t>
+          <t>6,16; 16,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 11,84</t>
+          <t>1,99; 10,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 9,55</t>
+          <t>4,0; 9,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 14,33</t>
+          <t>7,2; 14,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 11,97</t>
+          <t>5,55; 12,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 8,02</t>
+          <t>3,39; 9,21</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,78</t>
+          <t>0,0; 6,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 13,79</t>
+          <t>3,85; 14,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,18</t>
+          <t>0,0; 4,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,08</t>
+          <t>1,71; 11,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 7,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 15,37</t>
+          <t>3,18; 14,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,92</t>
+          <t>0,0; 7,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 13,76</t>
+          <t>2,39; 13,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,83</t>
+          <t>0,52; 4,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 12,77</t>
+          <t>4,7; 12,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,53</t>
+          <t>0,48; 4,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 11,27</t>
+          <t>3,24; 10,49</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4,19%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,57%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,68%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 9,85</t>
+          <t>3,95; 14,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,15</t>
+          <t>1,57; 11,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,74</t>
+          <t>3,25; 13,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 9,28</t>
+          <t>0,0; 9,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 14,41</t>
+          <t>1,56; 9,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 10,71</t>
+          <t>0,83; 8,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 13,66</t>
+          <t>0,74; 9,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,73</t>
+          <t>0,73; 11,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 10,2</t>
+          <t>3,53; 9,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,15; 8,19</t>
+          <t>2,01; 7,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 9,45</t>
+          <t>3,05; 9,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,25</t>
+          <t>1,13; 7,92</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,18%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>9,27%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,11</t>
+          <t>0,0; 7,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 21,1</t>
+          <t>3,16; 17,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 17,66</t>
+          <t>1,38; 12,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 16,12</t>
+          <t>4,13; 18,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,51</t>
+          <t>0,0; 9,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 17,23</t>
+          <t>4,91; 21,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,21; 11,51</t>
+          <t>4,16; 19,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 17,8</t>
+          <t>2,27; 16,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,72</t>
+          <t>0,72; 6,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 15,21</t>
+          <t>4,73; 15,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,69</t>
+          <t>3,51; 12,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 14,45</t>
+          <t>4,59; 14,52</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2,78%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,85%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,47</t>
+          <t>0,0; 7,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,96</t>
+          <t>0,0; 8,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 7,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 16,02</t>
+          <t>2,74; 13,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,59</t>
+          <t>0,0; 9,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,2</t>
+          <t>0,0; 9,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,5</t>
+          <t>0,0; 6,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,25; 13,27</t>
+          <t>3,08; 16,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,29</t>
+          <t>0,76; 6,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,35</t>
+          <t>0,65; 6,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,7; 11,9</t>
+          <t>3,59; 11,69</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11,04%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3,46%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,89%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,58</t>
+          <t>0,96; 5,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,01</t>
+          <t>0,51; 5,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,88</t>
+          <t>0,45; 4,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,32; 14,27</t>
+          <t>7,03; 16,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,51</t>
+          <t>2,22; 9,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,4</t>
+          <t>1,48; 6,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,32</t>
+          <t>1,01; 5,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 15,97</t>
+          <t>5,85; 15,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,67</t>
+          <t>2,06; 5,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,91</t>
+          <t>1,43; 4,63</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,25</t>
+          <t>1,2; 4,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,01; 13,37</t>
+          <t>7,39; 13,78</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5,67%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>4,27%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>6,96%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,29; 7,25</t>
+          <t>5,37; 12,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,75</t>
+          <t>2,34; 7,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,43; 10,72</t>
+          <t>1,98; 7,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,74</t>
+          <t>2,85; 9,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 13,03</t>
+          <t>1,99; 7,27</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,25; 7,41</t>
+          <t>1,65; 6,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,3; 7,52</t>
+          <t>4,34; 10,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,63</t>
+          <t>1,25; 5,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,77</t>
+          <t>4,44; 8,57</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,13</t>
+          <t>2,61; 6,1</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,81</t>
+          <t>3,83; 7,81</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,28</t>
+          <t>2,63; 6,67</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>4,47%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>5,44%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,77</t>
+          <t>3,79; 6,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,12</t>
+          <t>4,81; 7,69</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,05; 6,7</t>
+          <t>3,27; 5,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,1</t>
+          <t>5,11; 8,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,3</t>
+          <t>3,22; 5,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,77</t>
+          <t>4,19; 7,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,79</t>
+          <t>4,03; 6,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,08</t>
+          <t>4,46; 7,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,71</t>
+          <t>3,84; 5,62</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,96</t>
+          <t>4,8; 6,85</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,77</t>
+          <t>4,04; 5,97</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,02; 7,18</t>
+          <t>5,13; 7,51</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2075</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7882</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6179</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1529</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>3680</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>4396</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1380</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3420</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7882</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6179</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5251</t>
+          <t>4597</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1480; 7392</t>
+          <t>680; 6321</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1608; 9226</t>
+          <t>4154; 13104</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4838</t>
+          <t>2846; 11724</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1263; 7767</t>
+          <t>0; 5679</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4936</t>
+          <t>1641; 7735</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4260; 13708</t>
+          <t>1572; 9073</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2755; 11602</t>
+          <t>0; 4958</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5878</t>
+          <t>1127; 6591</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2631; 10469</t>
+          <t>2865; 10587</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7700; 19183</t>
+          <t>7658; 19927</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3805; 13839</t>
+          <t>3823; 13006</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1924; 10462</t>
+          <t>1871; 9230</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7114</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12759</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6721</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7472</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6263</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9519</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11402</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5139</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7114</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12759</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6721</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>12615</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3209; 10707</t>
+          <t>3837; 12213</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5422; 14820</t>
+          <t>8197; 19126</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6670; 17170</t>
+          <t>3323; 11950</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1865; 11208</t>
+          <t>3846; 13456</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3836; 11803</t>
+          <t>3146; 10659</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7848; 19322</t>
+          <t>5544; 15661</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3344; 12020</t>
+          <t>6408; 16798</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4646; 15107</t>
+          <t>1999; 10463</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8436; 20080</t>
+          <t>8409; 19948</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16411; 30941</t>
+          <t>15535; 30507</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12787; 25644</t>
+          <t>11895; 25959</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7921; 20405</t>
+          <t>7328; 19923</t>
         </is>
       </c>
     </row>
@@ -2494,37 +2494,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5823</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1514</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>5002</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1385</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5823</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3802</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7060</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5262</t>
+          <t>0; 4298</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2109; 9404</t>
+          <t>2746; 10537</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4799</t>
+          <t>0; 3440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1586; 8788</t>
+          <t>1017; 6737</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4289</t>
+          <t>0; 5295</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2774; 10953</t>
+          <t>2170; 10052</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3436</t>
+          <t>0; 5185</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1292; 9243</t>
+          <t>1350; 7707</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>719; 6657</t>
+          <t>719; 6536</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6302; 17800</t>
+          <t>6548; 17777</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658; 6189</t>
+          <t>658; 6252</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4257; 14132</t>
+          <t>3755; 12164</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6295</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3881</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5953</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2165</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3135</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2779</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2833</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2445</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6295</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3881</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5953</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4791</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1166; 7374</t>
+          <t>3121; 11476</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>632; 6341</t>
+          <t>1269; 8902</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>803; 6729</t>
+          <t>2636; 10924</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>584; 6507</t>
+          <t>0; 6922</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3254; 11401</t>
+          <t>1166; 7314</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1217; 8655</t>
+          <t>649; 6904</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2746; 11089</t>
+          <t>570; 6961</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 7600</t>
+          <t>520; 8316</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5495; 15704</t>
+          <t>5438; 15124</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3414; 12981</t>
+          <t>3182; 11571</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4859; 14938</t>
+          <t>4826; 14738</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1608; 10749</t>
+          <t>1612; 11325</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3721</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3694</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1333</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4620</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>4027</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2530</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6288</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4649</t>
+          <t>0; 3361</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2113; 9264</t>
+          <t>1479; 8266</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1412; 7672</t>
+          <t>642; 5806</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>994; 5565</t>
+          <t>1633; 7453</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3369</t>
+          <t>0; 4157</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1373; 8054</t>
+          <t>2154; 9519</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>562; 5334</t>
+          <t>1808; 8591</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1135; 7249</t>
+          <t>808; 5715</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>619; 4959</t>
+          <t>620; 5469</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4289; 13790</t>
+          <t>4284; 13814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3070; 10498</t>
+          <t>3152; 11103</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3170; 10873</t>
+          <t>3448; 10914</t>
         </is>
       </c>
     </row>
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3046</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1560</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1597</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3677</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1272</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1375</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>6824</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5309</t>
+          <t>0; 4480</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5014</t>
+          <t>0; 5407</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3656</t>
+          <t>0; 4579</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1644; 7395</t>
+          <t>1342; 6735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3935</t>
+          <t>0; 5227</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4940</t>
+          <t>0; 5397</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4909</t>
+          <t>0; 3301</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1267; 7456</t>
+          <t>1409; 7456</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>884; 7283</t>
+          <t>885; 7170</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>751; 7384</t>
+          <t>754; 7246</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5463</t>
+          <t>0; 6039</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3785; 12180</t>
+          <t>3397; 11069</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3394</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2973</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2714</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>15542</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>6178</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>4793</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>3969</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>11412</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3394</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2973</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2714</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>27525</t>
+          <t>27109</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3324; 11039</t>
+          <t>1302; 8104</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2043; 9729</t>
+          <t>741; 7512</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1344; 8075</t>
+          <t>651; 6153</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6627; 17770</t>
+          <t>9905; 23314</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1294; 7477</t>
+          <t>2856; 11692</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>662; 7783</t>
+          <t>2059; 9546</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>663; 6229</t>
+          <t>1392; 8117</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>10443; 24795</t>
+          <t>7166; 18519</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4870; 14977</t>
+          <t>5450; 15666</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4135; 13876</t>
+          <t>4038; 13082</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3393; 11970</t>
+          <t>3376; 12219</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19622; 37419</t>
+          <t>19470; 36279</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>14091</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>7687</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7320</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>9035</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>6749</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>5916</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>11429</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>4701</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>14091</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>7687</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>7320</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13125</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3624; 11440</t>
+          <t>8809; 20143</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2631; 11035</t>
+          <t>4015; 13375</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>7268; 17597</t>
+          <t>3391; 12388</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2262; 8876</t>
+          <t>4543; 14906</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8998; 21383</t>
+          <t>3144; 11487</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3851; 12696</t>
+          <t>2702; 10879</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3928; 12841</t>
+          <t>7117; 16974</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>4843; 15105</t>
+          <t>1758; 7758</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14828; 28229</t>
+          <t>14281; 27578</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>7814; 20538</t>
+          <t>8742; 20412</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13156; 26174</t>
+          <t>12846; 26181</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8573; 21008</t>
+          <t>7874; 20013</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>58</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>36130</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>46100</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>32886</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>45633</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>30410</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>38621</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>37065</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>37437</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>36130</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>46100</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>32886</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>48417</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>85854</t>
+          <t>82409</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>22650; 39327</t>
+          <t>27358; 46481</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>29857; 50555</t>
+          <t>36103; 57724</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28561; 47171</t>
+          <t>24341; 43080</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28000; 47236</t>
+          <t>35761; 58317</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>27185; 45549</t>
+          <t>21917; 39561</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36046; 58334</t>
+          <t>29760; 50695</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24044; 43119</t>
+          <t>28392; 46841</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>37418; 61482</t>
+          <t>28041; 47758</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>54060; 80167</t>
+          <t>53897; 78900</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>71740; 101689</t>
+          <t>70068; 100074</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57615; 83620</t>
+          <t>58617; 86489</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>71550; 102444</t>
+          <t>68193; 99884</t>
         </is>
       </c>
     </row>
